--- a/data/trans_orig/IP19C07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>36538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43834</t>
+          <t>44126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37656</t>
+          <t>37556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42269</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>76789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85328</t>
+          <t>85303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17694</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60096</t>
+          <t>62320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195197</t>
+          <t>195703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>210628</t>
+          <t>210728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212428</t>
+          <t>211729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227864</t>
+          <t>227305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>413949</t>
+          <t>411725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434839</t>
+          <t>434361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>29430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57247</t>
+          <t>57051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68278</t>
+          <t>68115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57760</t>
+          <t>58382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67860</t>
+          <t>67679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119580</t>
+          <t>119370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133706</t>
+          <t>133403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94353</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297214</t>
+          <t>297809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317682</t>
+          <t>316795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315738</t>
+          <t>315423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334592</t>
+          <t>333558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618308</t>
+          <t>618565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>646219</t>
+          <t>646042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46368</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35156</t>
+          <t>35254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41825</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87564</t>
+          <t>87319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45205</t>
+          <t>46408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197235</t>
+          <t>197632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209871</t>
+          <t>209759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214365</t>
+          <t>214006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>228220</t>
+          <t>228132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416186</t>
+          <t>414983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434756</t>
+          <t>435082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21162</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37272</t>
+          <t>36825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65906</t>
+          <t>66598</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>77404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>61195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>72724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131138</t>
+          <t>131585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147248</t>
+          <t>146959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47275</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58006</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>84678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310733</t>
+          <t>310867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328970</t>
+          <t>328874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>318727</t>
+          <t>319264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337950</t>
+          <t>338256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635712</t>
+          <t>636051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>662723</t>
+          <t>662412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>533</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23258</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27592</t>
+          <t>27608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43801</t>
+          <t>43818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49467</t>
+          <t>49661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26736</t>
+          <t>26375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20278</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>38915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>226365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>240270</t>
+          <t>240236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235559</t>
+          <t>236357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246522</t>
+          <t>246448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466690</t>
+          <t>465994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>484631</t>
+          <t>484235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>27889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70924</t>
+          <t>71847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82274</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72723</t>
+          <t>73111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82608</t>
+          <t>82544</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147611</t>
+          <t>148327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162801</t>
+          <t>163277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>323424</t>
+          <t>323401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342023</t>
+          <t>341848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338732</t>
+          <t>339054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353151</t>
+          <t>353520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668499</t>
+          <t>668272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691661</t>
+          <t>690667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51029</t>
+          <t>50890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46402</t>
+          <t>46201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>237517</t>
+          <t>236866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250907</t>
+          <t>251238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295385</t>
+          <t>295540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311517</t>
+          <t>311625</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>538440</t>
+          <t>538641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>559860</t>
+          <t>559805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>31175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81228</t>
+          <t>80162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92642</t>
+          <t>92579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119997</t>
+          <t>119378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129989</t>
+          <t>129944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205043</t>
+          <t>204846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220465</t>
+          <t>220306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41294</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38966</t>
+          <t>38241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>45816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71610</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350339</t>
+          <t>350576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368447</t>
+          <t>369561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445478</t>
+          <t>446203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465045</t>
+          <t>464469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>804466</t>
+          <t>804047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830394</t>
+          <t>830260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6095</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10388</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10687</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5335</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -841,67 +841,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>40929</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37554</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>40831</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36538</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44126</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36239</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43700</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>87,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40929</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37556</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42258</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76789</t>
+          <t>76593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85303</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25062</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18077</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33809</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24392</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17594</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32619</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17496</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32179</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,68%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>25062</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18418</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>33994</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62320</t>
+          <t>60421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220661</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>211914</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>227646</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203930</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>195703</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>210728</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>196143</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>210826</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220661</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>211729</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>227305</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>411725</t>
+          <t>413624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434361</t>
+          <t>434262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5043</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14685</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12411</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7568</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18632</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8277</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19266</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9203</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5438</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14735</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29430</t>
+          <t>29201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63914</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>58432</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68074</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>63272</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57051</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68115</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>56417</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>67406</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63914</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>58382</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>67679</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119370</t>
+          <t>119599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133403</t>
+          <t>133217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27746</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46699</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>42898</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34135</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>53121</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32872</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>52969</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>28173</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46308</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>65315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94096</t>
+          <t>93057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>325504</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>315032</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>333985</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>308032</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>297809</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>316795</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>297961</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>318058</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>325504</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>315423</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>333558</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618565</t>
+          <t>619604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>646042</t>
+          <t>647346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7243</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3957</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1628</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8111</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3107</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7709</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39856</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35720</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41822</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44007</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39853</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46336</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39823</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46214</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39856</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35254</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42306</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78507</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87319</t>
+          <t>87129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18858</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12793</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28035</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16194</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10719</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22846</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10600</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23624</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18858</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12781</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26907</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46408</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>222055</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>212878</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>228120</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204284</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>197632</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>209759</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>196854</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>209878</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>222055</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>214006</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>228132</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414983</t>
+          <t>416499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>435082</t>
+          <t>435375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14188</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9339</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20233</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14186</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8880</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19686</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9048</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21212</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14188</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9401</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20930</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21451</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36825</t>
+          <t>37771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61892</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>72786</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72098</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66598</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77404</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65072</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>77236</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67937</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61195</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>72724</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>82,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131585</t>
+          <t>130639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146959</t>
+          <t>147253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86284</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86284</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86284</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27652</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46512</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>34337</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25853</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43860</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>44516</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36153</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27746</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46738</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84678</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>329849</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>319490</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>338350</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>455</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>320390</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>310867</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>328874</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>310211</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>328357</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>329849</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>319264</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>338256</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636051</t>
+          <t>635121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>662412</t>
+          <t>662378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>505</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>354727</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>354727</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>354727</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1777</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>836</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3808</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1777</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26364</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23256</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27599</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21303</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18331</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18811</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>84,97%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26364</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23366</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27608</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>83,03%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>69</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>44179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49661</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9788</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16544</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18536</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12504</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26375</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12921</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26216</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9788</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5722</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15813</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38915</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>242382</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>235626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>246687</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>234204</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>226365</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>240236</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>226524</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>239819</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>242382</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>236357</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>246448</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465994</t>
+          <t>466568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>484235</t>
+          <t>483715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252170</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4620,67 +4620,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14545</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>10320</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6025</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16671</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5885</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17530</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5154</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14587</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27889</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78367</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73153</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82361</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>78198</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71847</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>82493</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70988</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>82633</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,34%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78367</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73111</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82544</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148327</t>
+          <t>148347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163277</t>
+          <t>162880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>88518</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>88518</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>88518</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15014</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29636</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>39995</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21653</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>40170</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14488</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28954</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>40567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>63057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>347113</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>338372</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>352994</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>487</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>333704</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>323401</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>341848</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>323226</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>341743</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>347113</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>339054</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>353520</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668272</t>
+          <t>668348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>690667</t>
+          <t>690838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>363396</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>363396</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>363396</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4316</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4324</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28420</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>25378</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23051</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26643</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>86,52%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25484</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>66</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>53904</t>
+          <t>49668</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>46777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17751</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10572</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26154</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16737</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10589</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24961</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27475</t>
+          <t>27345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>35300</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46201</t>
+          <t>47014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>291794</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>283391</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>298973</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>245090</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>236866</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>251238</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>305278</t>
+          <t>248503</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295540</t>
+          <t>238707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311625</t>
+          <t>254649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>550368</t>
+          <t>540297</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>538641</t>
+          <t>528583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>559805</t>
+          <t>550507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10163</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5599</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16255</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12311</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7497</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19914</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117097</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>111005</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>121661</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>87765</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80162</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>92579</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>87,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>90928</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119378</t>
+          <t>83925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129944</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>213567</t>
+          <t>208025</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204846</t>
+          <t>198087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220306</t>
+          <t>215476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27914</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19800</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38307</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22072</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41057</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38241</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59383</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>45499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72029</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>433181</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>422788</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>441295</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>514</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>361275</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>350576</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>369561</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>456564</t>
+          <t>364809</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446203</t>
+          <t>353368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464469</t>
+          <t>373431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>817838</t>
+          <t>797989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>804047</t>
+          <t>784312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830260</t>
+          <t>811873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
